--- a/information_request_forms/049_personal_financial_snapshot_pdf--information_request_forms.xlsx
+++ b/information_request_forms/049_personal_financial_snapshot_pdf--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'ca'}</t>
+          <t>ca</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'CA'}</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'tx'}</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'TX'}</t>
+          <t>TX</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'ny'}</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'NY'}</t>
+          <t>NY</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'il'}</t>
+          <t>il</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'IL'}</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'self-employed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Self-employed'}</t>
+          <t>Self-employed</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'bank'}</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Bank'}</t>
+          <t>Bank</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'insurance'}</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Insurance'}</t>
+          <t>Insurance</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'financial_advisor'}</t>
+          <t>financial_advisor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Financial Advisor'}</t>
+          <t>Financial Advisor</t>
         </is>
       </c>
     </row>
